--- a/site/ADP-Workforce-Now-ServiceNow-Integration-Guide/headings.xlsx
+++ b/site/ADP-Workforce-Now-ServiceNow-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -504,6 +504,72 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Create Integration</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>h_01HXY3TX2QHXF1YJK3GCQQ87P7</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-ServiceNow-Integration-Guide/#h_01HXY3TX2QHXF1YJK3GCQQ87P7</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Configuration</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>h_01JPQ8ZTEY7NJC2SRMDWPK964A</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-ServiceNow-Integration-Guide/#h_01JPQ8ZTEY7NJC2SRMDWPK964A</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Applications</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>h_01JPQ91FKVZHN9SQJEN1N0S3XQ</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-ServiceNow-Integration-Guide/#h_01JPQ91FKVZHN9SQJEN1N0S3XQ</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/site/ADP-Workforce-Now-ServiceNow-Integration-Guide/headings.xlsx
+++ b/site/ADP-Workforce-Now-ServiceNow-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -570,6 +570,50 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Parameters</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>h_01JPS6V3Y0HBETQWCMNHNHZAVN</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-ServiceNow-Integration-Guide/#h_01JPS6V3Y0HBETQWCMNHNHZAVN</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Integration Features</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>h_01K04AVZNHW4RD086HGMDCJSM6</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-ServiceNow-Integration-Guide/#h_01K04AVZNHW4RD086HGMDCJSM6</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
